--- a/Validate_ANOVA_ManyTest.xlsx
+++ b/Validate_ANOVA_ManyTest.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANOVA_Cost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANOVA_FillRate" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tukey_Cost" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tukey_FillRate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descriptive" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ANOVA_Cost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ANOVA_FillRate" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tukey_Cost" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tukey_FillRate" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Descriptive" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,13 +730,13 @@
         <v>4</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>260110619957.2058</v>
+        <v>1999701182.593675</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1897613794.819576</v>
+        <v>40525952.8327267</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>262008233752.0254</v>
+        <v>2040227135.426401</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>3</v>
@@ -745,16 +745,16 @@
         <v>16</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>86703539985.73528</v>
+        <v>666567060.8645582</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>118600862.1762235</v>
+        <v>2532872.052045419</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>731.0532014253635</v>
+        <v>263.16649525438</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>2.51934790540681e-17</v>
+        <v>8.018936044205768e-14</v>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.9927574268653879</v>
+        <v>0.9801365484611806</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -788,13 +788,13 @@
         <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6093849173.946471</v>
+        <v>35720417.54881488</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>898803886.955673</v>
+        <v>3153953.181922234</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6992653060.902144</v>
+        <v>38874370.73073711</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>3</v>
@@ -803,16 +803,16 @@
         <v>16</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>2031283057.982157</v>
+        <v>11906805.84960496</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>56175242.93472956</v>
+        <v>197122.0738701396</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>36.1597556479163</v>
+        <v>60.4032091172548</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>2.340856040508056e-07</v>
+        <v>6.037052714383057e-09</v>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.871464538691168</v>
+        <v>0.9188680582441306</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
@@ -846,13 +846,13 @@
         <v>4</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>171800153107.2621</v>
+        <v>868195469.1428106</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>7345348252.210854</v>
+        <v>115436304.761923</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>179145501359.4729</v>
+        <v>983631773.9047335</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>3</v>
@@ -861,16 +861,16 @@
         <v>16</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>57266717702.42069</v>
+        <v>289398489.7142702</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>459084265.7631783</v>
+        <v>7214769.047620187</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>124.741190176102</v>
+        <v>40.11195477001839</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>2.617799593023155e-11</v>
+        <v>1.136827015018311e-07</v>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.9589978637673313</v>
+        <v>0.8826427654896972</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>15989856304.63802</v>
+        <v>4459475066.747625</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4597856163.761648</v>
+        <v>4076804002.057249</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>20587712468.39967</v>
+        <v>8536279068.804874</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>3</v>
@@ -919,24 +919,24 @@
         <v>16</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>5329952101.546006</v>
+        <v>1486491688.915875</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>287366010.235103</v>
+        <v>254800250.1285781</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>18.54760796931206</v>
+        <v>5.833949096069392</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>1.849406979714727e-05</v>
+        <v>0.006848902972401348</v>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>**</t>
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7766698864276955</v>
+        <v>0.5224143951718271</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>3.471973747025765</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.04100695208333998</v>
+        <v>0.04100695208333996</v>
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>86.11918489057075</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>4.349218256529163e-10</v>
+        <v>4.34921825652916e-10</v>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>410.540041198306</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2.428615467873803e-15</v>
+        <v>2.428615467873804e-15</v>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
@@ -1136,13 +1136,13 @@
         <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>49393498375.58094</v>
+        <v>34530447342.16971</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1434160499.077895</v>
+        <v>1888232445.743445</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>50827658874.65884</v>
+        <v>36418679787.91315</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>3</v>
@@ -1151,16 +1151,16 @@
         <v>16</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>16464499458.52698</v>
+        <v>11510149114.05657</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>89635031.19236846</v>
+        <v>118014527.8589653</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>183.6837588999328</v>
+        <v>97.53162871449136</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>1.324379816933732e-12</v>
+        <v>1.702748076033798e-10</v>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.9717838568442717</v>
+        <v>0.9481520896215979</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         <v>4</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>27256991814.62807</v>
+        <v>598973516.7503971</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3175827849.650524</v>
+        <v>1072613264.228264</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>30432819664.2786</v>
+        <v>1671586780.978661</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>3</v>
@@ -1209,33 +1209,33 @@
         <v>16</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>9085663938.209358</v>
+        <v>199657838.916799</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>198489240.6031578</v>
+        <v>67038329.01426651</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>45.77408785786258</v>
+        <v>2.978263955151828</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4.472183354607115e-08</v>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>***</t>
+        <v>0.06273371612164513</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.8956446400732876</v>
+        <v>0.3583263062176868</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="P13" s="9" t="inlineStr">
-        <is>
-          <t>Reject H0 — model means differ</t>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Fail to reject H0</t>
         </is>
       </c>
     </row>
@@ -1252,13 +1252,13 @@
         <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>6145801165.043046</v>
+        <v>3049276784.551012</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>17206873976.06316</v>
+        <v>17150487544.64944</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>23352675141.10621</v>
+        <v>20199764329.20045</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>3</v>
@@ -1267,16 +1267,16 @@
         <v>16</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>2048600388.347682</v>
+        <v>1016425594.850337</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1075429623.503948</v>
+        <v>1071905471.54059</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>1.904913481621382</v>
+        <v>0.9482418196722916</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.1695111583228869</v>
+        <v>0.440745358446903</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2631733250219795</v>
+        <v>0.1509560574497905</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         <v>4</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3117.575781244001</v>
+        <v>18.64309712399999</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>58.80894548800002</v>
+        <v>1.384504616000014</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>3176.384726732001</v>
+        <v>20.02760174000001</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>3</v>
@@ -1453,16 +1453,16 @@
         <v>16</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1039.191927081333</v>
+        <v>6.214365707999998</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>3.675559093000001</v>
+        <v>0.08653153850000089</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>282.7303005576606</v>
+        <v>71.81619344488998</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>4.571158794089305e-14</v>
+        <v>1.686931061659913e-09</v>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.9814855722629968</v>
+        <v>0.9308701743736585</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -1496,13 +1496,13 @@
         <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1305.8800705135</v>
+        <v>0.0437724060000021</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>13.73134711200001</v>
+        <v>0.0313470120000013</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1319.611417625501</v>
+        <v>0.07511941800000341</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>3</v>
@@ -1511,24 +1511,24 @@
         <v>16</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>435.2933568378335</v>
+        <v>0.0145908020000007</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.8582091945000008</v>
+        <v>0.001959188250000082</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>507.2112482917911</v>
+        <v>7.447371124239507</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>4.567371058143465e-16</v>
+        <v>0.002433449089669719</v>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>**</t>
         </is>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.9895944011027821</v>
+        <v>0.5827042749452627</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
@@ -1554,13 +1554,13 @@
         <v>4</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>209.7992243059992</v>
+        <v>14.77167554400015</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>59.80766953599991</v>
+        <v>0.5750065279999925</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>269.6068938419992</v>
+        <v>15.34668207200014</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>3</v>
@@ -1569,16 +1569,16 @@
         <v>16</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>69.93307476866642</v>
+        <v>4.923891848000049</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>3.737979345999995</v>
+        <v>0.03593790799999953</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>18.70879111290486</v>
+        <v>137.0110872341277</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>1.753970356158491e-05</v>
+        <v>1.274846119172393e-11</v>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.7781671355516239</v>
+        <v>0.9625321926066948</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1028.283395292001</v>
+        <v>1059.953064370001</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>13.78181347999997</v>
+        <v>7.839509107999994</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1042.065208772001</v>
+        <v>1067.792573478001</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>3</v>
@@ -1627,16 +1627,16 @@
         <v>16</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>342.7611317640003</v>
+        <v>353.3176881233338</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.8613633424999982</v>
+        <v>0.4899693192499996</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>397.9286264599779</v>
+        <v>721.1016572714469</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>3.106499663517655e-15</v>
+        <v>2.808934016870164e-17</v>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.9867745191337489</v>
+        <v>0.9926582097471748</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>234.8382483058622</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>1.954497005739311e-13</v>
+        <v>1.954497005739312e-13</v>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         <v>0.4793068372500016</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>522.9875131040944</v>
+        <v>522.9875131040867</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>3.584247748157513e-16</v>
+        <v>3.584247748157936e-16</v>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
@@ -1844,13 +1844,13 @@
         <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1015.9515990135</v>
+        <v>1001.722360451998</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>10.019018144</v>
+        <v>10.60981230000001</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1025.9706171575</v>
+        <v>1012.332172751998</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>3</v>
@@ -1859,16 +1859,16 @@
         <v>16</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>338.6505330044999</v>
+        <v>333.9074534839995</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.6261886340000001</v>
+        <v>0.6631132687500003</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>540.8123281338561</v>
+        <v>503.5451245206268</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2.74900962508139e-16</v>
+        <v>4.837180924804137e-16</v>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.9902345954392356</v>
+        <v>0.9895194358279086</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -1902,13 +1902,13 @@
         <v>4</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>599.5734376099995</v>
+        <v>37.71086639350037</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3.748784580000013</v>
+        <v>1.817054575999995</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>603.3222221899995</v>
+        <v>39.52792096950036</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>3</v>
@@ -1917,16 +1917,16 @@
         <v>16</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>199.8578125366665</v>
+        <v>12.57028879783346</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.2342990362500008</v>
+        <v>0.1135659109999997</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>853.0031353753486</v>
+        <v>110.6871656040643</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>7.397315696309109e-18</v>
+        <v>6.519270865239196e-11</v>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.9937864304643176</v>
+        <v>0.9540311118967771</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -1960,13 +1960,13 @@
         <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1071.491140504002</v>
+        <v>1063.887442841502</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>6.810994823999985</v>
+        <v>12.06332860799998</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1078.302135328002</v>
+        <v>1075.950771449502</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>3</v>
@@ -1975,16 +1975,16 @@
         <v>16</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>357.1637135013339</v>
+        <v>354.6291476138339</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.425687176499999</v>
+        <v>0.7539580379999991</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>839.0285947487364</v>
+        <v>470.356611031762</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>8.435009368259593e-18</v>
+        <v>8.29412493427086e-16</v>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.9936835933076138</v>
+        <v>0.9887882151041647</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2121,28 +2121,28 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>11767.11598</v>
+        <v>55269.7481</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>264227.33266</v>
+        <v>65732.06165999999</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-252460.21668</v>
+        <v>-10462.31355999999</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>252460.21668</v>
+        <v>10462.31355999999</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>19705.83256057146</v>
+        <v>2879.767931543484</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>8.901894876789385e-08</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-272166.0492405714</v>
+        <v>-13342.08149154347</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-232754.3841194285</v>
+        <v>-7582.545628456504</v>
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
@@ -2163,28 +2163,28 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>11767.11598</v>
+        <v>55269.7481</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>262185.04354</v>
+        <v>65769.2102</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-250417.92756</v>
+        <v>-10499.4621</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>250417.92756</v>
+        <v>10499.4621</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>19705.83256057146</v>
+        <v>2879.767931543484</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>8.470433787710618e-08</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-270123.7601205714</v>
+        <v>-13379.23003154348</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-230712.0949994285</v>
+        <v>-7619.694168456514</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -2205,28 +2205,28 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>11767.11598</v>
+        <v>55269.7481</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>294123.57576</v>
+        <v>83128.25876</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-282356.45978</v>
+        <v>-27858.51065999999</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>282356.45978</v>
+        <v>27858.51065999999</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>19705.83256057146</v>
+        <v>2879.767931543484</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0</v>
+        <v>3.419486915845482e-14</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>-302062.2923405715</v>
+        <v>-30738.27859154348</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-262650.6272194286</v>
+        <v>-24978.74272845651</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -2247,28 +2247,28 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>264227.33266</v>
+        <v>65732.06165999999</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>262185.04354</v>
+        <v>65769.2102</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2042.289119999972</v>
+        <v>-37.14854000000923</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2042.289119999972</v>
+        <v>37.14854000000923</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>19705.83256057146</v>
+        <v>2879.767931543484</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.9905790972620069</v>
+        <v>0.9999811242308545</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-17663.54344057148</v>
+        <v>-2916.916471543493</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>21748.12168057143</v>
+        <v>2842.619391543475</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -2289,32 +2289,32 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>264227.33266</v>
+        <v>65732.06165999999</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>294123.57576</v>
+        <v>83128.25876</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-29896.24310000008</v>
+        <v>-17396.1971</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>29896.24310000008</v>
+        <v>17396.1971</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>19705.83256057146</v>
+        <v>2879.767931543484</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.00256296263403244</v>
+        <v>5.053280016653616e-11</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-49602.07566057154</v>
+        <v>-20275.96503154349</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-10190.41053942862</v>
+        <v>-14516.42916845652</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>***</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2331,32 +2331,32 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>262185.04354</v>
+        <v>65769.2102</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>294123.57576</v>
+        <v>83128.25876</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-31938.53222000005</v>
+        <v>-17359.04856</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>31938.53222000005</v>
+        <v>17359.04856</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>19705.83256057146</v>
+        <v>2879.767931543484</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.001407665336451758</v>
+        <v>5.220357479629456e-11</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-51644.36478057151</v>
+        <v>-20238.81649154348</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-12232.6996594286</v>
+        <v>-14479.28062845651</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>***</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -2377,28 +2377,28 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>71590.54244</v>
+        <v>73949.04883999999</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>105435.04684</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-33844.50440000001</v>
+        <v>2399.223299999983</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>33844.50440000001</v>
+        <v>2399.223299999983</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>13561.9876583867</v>
+        <v>803.3753368416096</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.278135610949249e-05</v>
+        <v>1.288426856649316e-06</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-47406.49205838671</v>
+        <v>1595.847963158374</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-20282.5167416133</v>
+        <v>3202.598636841593</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -2419,28 +2419,28 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>71590.54244</v>
+        <v>73949.04883999999</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>109947.82728</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-38357.28483999999</v>
+        <v>2399.223299999983</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>38357.28483999999</v>
+        <v>2399.223299999983</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>13561.9876583867</v>
+        <v>803.3753368416096</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>2.627002658517341e-06</v>
+        <v>1.288426856649316e-06</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-51919.27249838669</v>
+        <v>1595.847963158374</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-24795.29718161329</v>
+        <v>3202.598636841593</v>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>HAPPO</t>
         </is>
       </c>
     </row>
@@ -2461,37 +2461,37 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>71590.54244</v>
+        <v>73949.04883999999</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>116941.21104</v>
+        <v>74449.27092000001</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-45350.66859999999</v>
+        <v>-500.2220800000214</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>45350.66859999999</v>
+        <v>500.2220800000214</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>13561.9876583867</v>
+        <v>803.3753368416096</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>2.809303951689657e-07</v>
+        <v>0.3174718179810077</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-58912.65625838669</v>
+        <v>-1303.597416841631</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-31788.68094161329</v>
-      </c>
-      <c r="K13" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
+        <v>303.1532568415882</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2503,28 +2503,28 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>105435.04684</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>109947.82728</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-4512.780439999988</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>4512.780439999988</v>
+        <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>13561.9876583867</v>
+        <v>803.3753368416096</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.777737456584596</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-18074.76809838669</v>
+        <v>-803.3753368416096</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>9049.207218386713</v>
+        <v>803.3753368416096</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -2545,37 +2545,37 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>105435.04684</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>116941.21104</v>
+        <v>74449.27092000001</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-11506.16419999998</v>
+        <v>-2899.445380000005</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>11506.16419999998</v>
+        <v>2899.445380000005</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>13561.9876583867</v>
+        <v>803.3753368416096</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.1116854573360571</v>
+        <v>9.765938946415531e-08</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-25068.15185838669</v>
+        <v>-3702.820716841614</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>2055.823458386716</v>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>n.s.</t>
+        <v>-2096.070043158395</v>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>***</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -2587,37 +2587,37 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>109947.82728</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>116941.21104</v>
+        <v>74449.27092000001</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-6993.383759999997</v>
+        <v>-2899.445380000005</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>6993.383759999997</v>
+        <v>2899.445380000005</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>13561.9876583867</v>
+        <v>803.3753368416096</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.4740925274555201</v>
+        <v>9.765938946415531e-08</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-20555.3714183867</v>
+        <v>-3702.820716841614</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>6568.603898386704</v>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>n.s.</t>
+        <v>-2096.070043158395</v>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>***</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HAPPO</t>
         </is>
       </c>
     </row>
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>174952.73972</v>
+        <v>87473.67942</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>364807.10478</v>
+        <v>102410.96022</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-189854.36506</v>
+        <v>-14937.28080000001</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>189854.36506</v>
+        <v>14937.28080000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>38770.11323205895</v>
+        <v>4860.288866774106</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.18817500283086e-09</v>
+        <v>8.800996931235261e-07</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-228624.4782920589</v>
+        <v>-19797.56966677411</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-151084.251827941</v>
+        <v>-10076.9919332259</v>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
@@ -2675,28 +2675,28 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>174952.73972</v>
+        <v>87473.67942</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>367803.24106</v>
+        <v>101424.45222</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-192850.50134</v>
+        <v>-13950.77280000001</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>192850.50134</v>
+        <v>13950.77280000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>38770.11323205895</v>
+        <v>4860.288866774106</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>9.415694890435589e-10</v>
+        <v>2.168242372979634e-06</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-231620.614572059</v>
+        <v>-18811.06166677411</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-154080.3881079411</v>
+        <v>-9090.4839332259</v>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
@@ -2717,37 +2717,37 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>174952.73972</v>
+        <v>87473.67942</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>417673.33198</v>
+        <v>90363.50659999999</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-242720.59226</v>
+        <v>-2889.827179999993</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>242720.59226</v>
+        <v>2889.827179999993</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>38770.11323205895</v>
+        <v>4860.288866774106</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>2.93153279429248e-11</v>
+        <v>0.3551467490361402</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-281490.7054920589</v>
+        <v>-7750.116046774099</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-203950.4790279411</v>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
+        <v>1970.461686774113</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2759,28 +2759,28 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>364807.10478</v>
+        <v>102410.96022</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>367803.24106</v>
+        <v>101424.45222</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-2996.136280000035</v>
+        <v>986.5080000000016</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>2996.136280000035</v>
+        <v>986.5080000000016</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>38770.11323205895</v>
+        <v>4860.288866774106</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0.9960263482260221</v>
+        <v>0.9364448952691771</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-41766.24951205899</v>
+        <v>-3873.780866774105</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>35773.97695205892</v>
+        <v>5846.796866774108</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -2801,37 +2801,37 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>364807.10478</v>
+        <v>102410.96022</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>417673.33198</v>
+        <v>90363.50659999999</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-52866.22720000002</v>
+        <v>12047.45362000001</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>52866.22720000002</v>
+        <v>12047.45362000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>38770.11323205895</v>
+        <v>4860.288866774106</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.006264332078591117</v>
+        <v>1.388609376262728e-05</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-91636.34043205898</v>
+        <v>7187.164753225908</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-14096.11396794107</v>
+        <v>16907.74248677412</v>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>MAPPO</t>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -2843,37 +2843,37 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>367803.24106</v>
+        <v>101424.45222</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>417673.33198</v>
+        <v>90363.50659999999</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-49870.09091999999</v>
+        <v>11060.94562000001</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>49870.09091999999</v>
+        <v>11060.94562000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>38770.11323205895</v>
+        <v>4860.288866774106</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.009820788430066174</v>
+        <v>3.874029622985553e-05</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-88640.20415205894</v>
+        <v>6200.656753225907</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-11099.97768794103</v>
+        <v>15921.23448677412</v>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>HAPPO</t>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -2889,37 +2889,37 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>170826.34104</v>
+        <v>243090.99876</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>209895.49308</v>
+        <v>226841.5428</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-39069.15203999996</v>
+        <v>16249.45596000002</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>39069.15203999996</v>
+        <v>16249.45596000002</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>30673.86941514793</v>
+        <v>28883.56463492421</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>0.01056642735988245</v>
+        <v>0.4012204653969764</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-69743.02145514789</v>
+        <v>-12634.10867492418</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-8395.282624852025</v>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>*</t>
+        <v>45133.02059492422</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>170826.34104</v>
+        <v>243090.99876</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>250769.89134</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-79943.55029999997</v>
+        <v>-7678.892579999985</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>79943.55029999997</v>
+        <v>7678.892579999985</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>30673.86941514793</v>
+        <v>28883.56463492421</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>7.454639182391531e-06</v>
+        <v>0.8708160625605271</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-110617.4197151479</v>
+        <v>-36562.45721492419</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-49269.68088485204</v>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
+        <v>21204.67205492422</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2973,37 +2973,37 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>170826.34104</v>
+        <v>243090.99876</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>212106.58592</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>-41280.24487999995</v>
+        <v>30984.41284000003</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>41280.24487999995</v>
+        <v>30984.41284000003</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>30673.86941514793</v>
+        <v>28883.56463492421</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.006948784427797561</v>
+        <v>0.03338836914873833</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-71954.11429514788</v>
+        <v>2100.848205075828</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>-10606.37546485202</v>
+        <v>59867.97747492424</v>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>(s,S) Policy</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -3015,37 +3015,37 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>209895.49308</v>
+        <v>226841.5428</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>250769.89134</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-40874.39826000002</v>
+        <v>-23928.34854000001</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>40874.39826000002</v>
+        <v>23928.34854000001</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>30673.86941514793</v>
+        <v>28883.56463492421</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>0.007505225488389611</v>
+        <v>0.1235433745718579</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>-71548.26767514794</v>
+        <v>-52811.91317492421</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-10200.52884485208</v>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>**</t>
+        <v>4955.216094924199</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>MAPPO</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3057,28 +3057,28 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>209895.49308</v>
+        <v>226841.5428</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>212106.58592</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-2211.092839999998</v>
+        <v>14734.95688000001</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2211.092839999998</v>
+        <v>14734.95688000001</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>30673.86941514793</v>
+        <v>28883.56463492421</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.996766063189124</v>
+        <v>0.4830005799514421</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>-32884.96225514793</v>
+        <v>-14148.60775492419</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>28462.77657514793</v>
+        <v>43618.52151492421</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
@@ -3111,20 +3111,20 @@
         <v>38663.30542000002</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>30673.86941514793</v>
+        <v>28883.56463492421</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0.01140903202696453</v>
+        <v>0.007245743671102978</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>7989.436004852087</v>
+        <v>9779.740785075814</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>69337.17483514795</v>
+        <v>67546.87005492422</v>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**</t>
         </is>
       </c>
       <c r="L28" s="16" t="inlineStr">
@@ -3913,28 +3913,28 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>56282.888</v>
+        <v>88719.47573999999</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>163584.76914</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>-107301.88114</v>
+        <v>-74865.29340000002</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>107301.88114</v>
+        <v>74865.29340000002</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>17131.27758465944</v>
+        <v>19657.06174480795</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>2.910161001068445e-11</v>
+        <v>4.578577494918079e-08</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>-124433.1587246595</v>
+        <v>-94522.35514480798</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-90170.60355534057</v>
+        <v>-55208.23165519207</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -3955,28 +3955,28 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>56282.888</v>
+        <v>88719.47573999999</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>163584.76914</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-107301.88114</v>
+        <v>-74865.29340000002</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>107301.88114</v>
+        <v>74865.29340000002</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>17131.27758465944</v>
+        <v>19657.06174480795</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>2.910161001068445e-11</v>
+        <v>4.578577494918079e-08</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-124433.1587246595</v>
+        <v>-94522.35514480798</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-90170.60355534057</v>
+        <v>-55208.23165519207</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -3997,37 +3997,37 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>56282.888</v>
+        <v>88719.47573999999</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>73621.48692</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>-17338.59892</v>
+        <v>15097.98882</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>17338.59892</v>
+        <v>15097.98882</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>17131.27758465944</v>
+        <v>19657.06174480795</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.04678208236333548</v>
+        <v>0.1661417197371656</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>-34469.87650465943</v>
+        <v>-4559.072924807951</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-207.3213353405554</v>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>*</t>
+        <v>34755.05056480795</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4051,16 +4051,16 @@
         <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>17131.27758465944</v>
+        <v>19657.06174480795</v>
       </c>
       <c r="H50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-17131.27758465944</v>
+        <v>-19657.06174480795</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>17131.27758465944</v>
+        <v>19657.06174480795</v>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
@@ -4093,16 +4093,16 @@
         <v>89963.28222000002</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>17131.27758465944</v>
+        <v>19657.06174480795</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>4.190489066857594e-10</v>
+        <v>3.225601785672438e-09</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>72832.00463534058</v>
+        <v>70306.22047519207</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>107094.5598046595</v>
+        <v>109620.343964808</v>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
@@ -4135,16 +4135,16 @@
         <v>89963.28222000002</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>17131.27758465944</v>
+        <v>19657.06174480795</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>4.190489066857594e-10</v>
+        <v>3.225601785672438e-09</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>72832.00463534058</v>
+        <v>70306.22047519207</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>107094.5598046595</v>
+        <v>109620.343964808</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
@@ -4157,267 +4157,10 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>4x30</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>(s,S) Policy vs MAPPO</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>332468.28218</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>431016.02148</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>-98547.73930000002</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>98547.73930000002</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>25492.90633407568</v>
-      </c>
-      <c r="H53" s="7" t="n">
-        <v>3.706505391498638e-08</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>-124040.6456340757</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>-73054.83296592435</v>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>(s,S) Policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="n"/>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>(s,S) Policy vs HAPPO</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>332468.28218</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>411428.11356</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>-78959.83137999999</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>78959.83137999999</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>25492.90633407568</v>
-      </c>
-      <c r="H54" s="7" t="n">
-        <v>7.931944778771793e-07</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>-104452.7377140757</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>-53466.92504592431</v>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>(s,S) Policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="n"/>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>(s,S) Policy vs GNN-HAPPO</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>332468.28218</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>388358.1053</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>-55889.82312000002</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>55889.82312000002</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>25492.90633407568</v>
-      </c>
-      <c r="H55" s="7" t="n">
-        <v>5.981238532237754e-05</v>
-      </c>
-      <c r="I55" s="5" t="n">
-        <v>-81382.72945407568</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>-30396.91678592434</v>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>(s,S) Policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="n"/>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>MAPPO vs HAPPO</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>431016.02148</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>411428.11356</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>19587.90792000003</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>19587.90792000003</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>25492.90633407568</v>
-      </c>
-      <c r="H56" s="7" t="n">
-        <v>0.1659050954396074</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>-5904.99841407565</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>45080.8142540757</v>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="n"/>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>MAPPO vs GNN-HAPPO</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>431016.02148</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>388358.1053</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>42657.91618</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>42657.91618</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>25492.90633407568</v>
-      </c>
-      <c r="H57" s="7" t="n">
-        <v>0.00104104251127235</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>17165.00984592432</v>
-      </c>
-      <c r="J57" s="5" t="n">
-        <v>68150.82251407567</v>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="L57" s="16" t="inlineStr">
-        <is>
-          <t>GNN-HAPPO</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="n"/>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>HAPPO vs GNN-HAPPO</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>411428.11356</v>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>388358.1053</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>23070.00825999997</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>23070.00825999997</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>25492.90633407568</v>
-      </c>
-      <c r="H58" s="7" t="n">
-        <v>0.0833543187015976</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>-2422.898074075703</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>48562.91459407565</v>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A53:A58"/>
     <mergeCell ref="A29:A34"/>
     <mergeCell ref="A11:A16"/>
     <mergeCell ref="A47:A52"/>
@@ -4540,28 +4283,28 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>95.52536000000001</v>
+        <v>97.74202</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>76.65346</v>
+        <v>100</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>18.87190000000001</v>
+        <v>-2.257980000000003</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>18.87190000000001</v>
+        <v>2.257980000000003</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>3.46906605922478</v>
+        <v>0.5322774625949531</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2.466772341946921e-10</v>
+        <v>9.762867292373301e-09</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>15.40283394077523</v>
+        <v>-2.790257462594957</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>22.34096605922479</v>
+        <v>-1.72570253740505</v>
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
@@ -4570,7 +4313,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -4582,28 +4325,28 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>95.52536000000001</v>
+        <v>97.74202</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>77.84826000000001</v>
+        <v>100</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>17.6771</v>
+        <v>-2.257980000000003</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>17.6771</v>
+        <v>2.257980000000003</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>3.46906605922478</v>
+        <v>0.5322774625949531</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>6.573527278064262e-10</v>
+        <v>9.762867292373301e-09</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>14.20803394077522</v>
+        <v>-2.790257462594957</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>21.14616605922478</v>
+        <v>-1.72570253740505</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -4612,7 +4355,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>HAPPO</t>
         </is>
       </c>
     </row>
@@ -4624,37 +4367,37 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>95.52536000000001</v>
+        <v>97.74202</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>35.28172</v>
+        <v>-0.8423600000000135</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>35.28172</v>
+        <v>0.8423600000000135</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>3.46906605922478</v>
+        <v>0.5322774625949531</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.543210004228968e-14</v>
+        <v>0.001754619949010605</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>31.81265394077522</v>
+        <v>-1.374637462594967</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>38.75078605922478</v>
+        <v>-0.3100825374050604</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>(s,S) Policy</t>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -4666,28 +4409,28 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>76.65346</v>
+        <v>100</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>77.84826000000001</v>
+        <v>100</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-1.194800000000015</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1.194800000000015</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>3.46906605922478</v>
+        <v>0.5322774625949531</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.7596350464967226</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-4.663866059224794</v>
+        <v>-0.5322774625949531</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>2.274266059224765</v>
+        <v>0.5322774625949531</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -4708,28 +4451,28 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>76.65346</v>
+        <v>100</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>16.40981999999999</v>
+        <v>1.41561999999999</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>16.40981999999999</v>
+        <v>1.41561999999999</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>3.46906605922478</v>
+        <v>0.5322774625949531</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.983299413588213e-09</v>
+        <v>5.776465223150673e-06</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>12.94075394077521</v>
+        <v>0.8833425374050368</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>19.87888605922477</v>
+        <v>1.947897462594943</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -4750,28 +4493,28 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>77.84826000000001</v>
+        <v>100</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>17.60462</v>
+        <v>1.41561999999999</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17.60462</v>
+        <v>1.41561999999999</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>3.46906605922478</v>
+        <v>0.5322774625949531</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>6.989057110828867e-10</v>
+        <v>5.776465223150673e-06</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>14.13555394077522</v>
+        <v>0.8833425374050368</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>21.07368605922478</v>
+        <v>1.947897462594943</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -4796,37 +4539,37 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>13.6606</v>
+        <v>-0.1080400000000026</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>13.6606</v>
+        <v>0.1080400000000026</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.676283409520527</v>
+        <v>0.08009196500939469</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>5.014877402231832e-13</v>
+        <v>0.00682166465877776</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>11.98431659047948</v>
+        <v>-0.1881319650093973</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>15.33688340952053</v>
+        <v>-0.02794803499060788</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>**</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -4838,37 +4581,37 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>13.39076</v>
+        <v>-0.1080400000000026</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>13.39076</v>
+        <v>0.1080400000000026</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.676283409520527</v>
+        <v>0.08009196500939469</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>6.841194277740215e-13</v>
+        <v>0.00682166465877776</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>11.71447659047947</v>
+        <v>-0.1881319650093973</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>15.06704340952053</v>
+        <v>-0.02794803499060788</v>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>**</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>HAPPO</t>
         </is>
       </c>
     </row>
@@ -4880,32 +4623,32 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-4.605260000000001</v>
+        <v>-0.1080400000000026</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>4.605260000000001</v>
+        <v>0.1080400000000026</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.676283409520527</v>
+        <v>0.08009196500939469</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>3.820552372579833e-06</v>
+        <v>0.00682166465877776</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-6.281543409520528</v>
+        <v>-0.1881319650093973</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-2.928976590479475</v>
+        <v>-0.02794803499060788</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>**</t>
         </is>
       </c>
       <c r="L13" s="16" t="inlineStr">
@@ -4922,28 +4665,28 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.2698400000000021</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.2698400000000021</v>
+        <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.676283409520527</v>
+        <v>0.08009196500939469</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.9665555217714383</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-1.946123409520529</v>
+        <v>-0.08009196500939469</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1.406443409520524</v>
+        <v>0.08009196500939469</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -4964,37 +4707,37 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-18.26586</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>18.26586</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.676283409520527</v>
+        <v>0.08009196500939469</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>5.10702591327572e-15</v>
+        <v>1</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>-19.94214340952053</v>
+        <v>-0.08009196500939469</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-16.58957659047948</v>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>GNN-HAPPO</t>
+        <v>0.08009196500939469</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5006,37 +4749,37 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-17.99602</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>17.99602</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.676283409520527</v>
+        <v>0.08009196500939469</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>6.439293542825908e-15</v>
+        <v>1</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-19.67230340952053</v>
+        <v>-0.08009196500939469</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-16.31973659047948</v>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>GNN-HAPPO</t>
+        <v>0.08009196500939469</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5052,28 +4795,28 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>86.72666</v>
+        <v>98.01527999999999</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>79.23348000000001</v>
+        <v>100</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>7.493179999999981</v>
+        <v>-1.98472000000001</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>7.493179999999981</v>
+        <v>1.98472000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3.498398788148229</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>7.807068473530965e-05</v>
+        <v>9.725564797946618e-11</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>3.994781211851752</v>
+        <v>-2.327746175673972</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>10.99157878814821</v>
+        <v>-1.641693824326048</v>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
@@ -5082,7 +4825,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -5094,28 +4837,28 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>86.72666</v>
+        <v>98.01527999999999</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>79.29212000000001</v>
+        <v>100</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7.434539999999984</v>
+        <v>-1.98472000000001</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>7.434539999999984</v>
+        <v>1.98472000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>3.498398788148229</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>8.534155251538333e-05</v>
+        <v>9.725564797946618e-11</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>3.936141211851755</v>
+        <v>-2.327746175673972</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>10.93293878814821</v>
+        <v>-1.641693824326048</v>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
@@ -5124,7 +4867,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>HAPPO</t>
         </is>
       </c>
     </row>
@@ -5136,37 +4879,37 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>86.72666</v>
+        <v>98.01527999999999</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>7.510639999999995</v>
+        <v>-1.98472000000001</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>7.510639999999995</v>
+        <v>1.98472000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3.498398788148229</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>7.603222657459607e-05</v>
+        <v>9.725564797946618e-11</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>4.012241211851766</v>
+        <v>-2.327746175673972</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>11.00903878814822</v>
+        <v>-1.641693824326048</v>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>(s,S) Policy</t>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -5178,28 +4921,28 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>79.23348000000001</v>
+        <v>100</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>79.29212000000001</v>
+        <v>100</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.05863999999999692</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.05863999999999692</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>3.498398788148229</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0.9999586053203013</v>
+        <v>1</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-3.557038788148226</v>
+        <v>-0.3430261756739617</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>3.439758788148232</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -5220,28 +4963,28 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>79.23348000000001</v>
+        <v>100</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.01746000000001402</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.01746000000001402</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3.498398788148229</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.9999989062939211</v>
+        <v>1</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-3.480938788148215</v>
+        <v>-0.3430261756739617</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>3.515858788148243</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -5262,28 +5005,28 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>79.29212000000001</v>
+        <v>100</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.07610000000001094</v>
+        <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.07610000000001094</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>3.498398788148229</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.9999095908343395</v>
+        <v>1</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-3.422298788148218</v>
+        <v>-0.3430261756739617</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>3.57449878814824</v>
+        <v>0.3430261756739617</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -5308,28 +5051,28 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>90.72194</v>
+        <v>90.27560000000001</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>78.11203999999999</v>
+        <v>77.29986</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>12.60990000000001</v>
+        <v>12.97574000000002</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>12.60990000000001</v>
+        <v>12.97574000000002</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.679360979007053</v>
+        <v>1.266587822974027</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>1.78823622576374e-12</v>
+        <v>1.376676550535194e-14</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>10.93053902099296</v>
+        <v>11.70915217702599</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>14.28926097900706</v>
+        <v>14.24232782297404</v>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
@@ -5350,28 +5093,28 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>90.72194</v>
+        <v>90.27560000000001</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>77.50592</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>13.21602</v>
+        <v>12.76968000000001</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>13.21602</v>
+        <v>12.76968000000001</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.679360979007053</v>
+        <v>1.266587822974027</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>8.633094239485217e-13</v>
+        <v>1.77635683940025e-14</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>11.53665902099295</v>
+        <v>11.50309217702598</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>14.89538097900705</v>
+        <v>14.03626782297403</v>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -5392,32 +5135,32 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>90.72194</v>
+        <v>90.27560000000001</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>93.32698000000001</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>-2.605040000000002</v>
+        <v>-3.051379999999995</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2.605040000000002</v>
+        <v>3.051379999999995</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.679360979007053</v>
+        <v>1.266587822974027</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.002103423609603694</v>
+        <v>1.964549027022588e-05</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-4.284400979007056</v>
+        <v>-4.317967822974022</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>-0.9256790209929493</v>
+        <v>-1.784792177025968</v>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>***</t>
         </is>
       </c>
       <c r="L25" s="16" t="inlineStr">
@@ -5434,28 +5177,28 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>78.11203999999999</v>
+        <v>77.29986</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>77.50592</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.60611999999999</v>
+        <v>-0.2060600000000079</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.60611999999999</v>
+        <v>0.2060600000000079</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.679360979007053</v>
+        <v>1.266587822974027</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>0.7333082344170745</v>
+        <v>0.9655433660947291</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>-1.073240979007063</v>
+        <v>-1.472647822974035</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>2.285480979007043</v>
+        <v>1.060527822974019</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -5476,28 +5219,28 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>78.11203999999999</v>
+        <v>77.29986</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>93.32698000000001</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-15.21494000000001</v>
+        <v>-16.02712000000001</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>15.21494000000001</v>
+        <v>16.02712000000001</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1.679360979007053</v>
+        <v>1.266587822974027</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>9.581224702515101e-14</v>
+        <v>3.33066907387547e-16</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>-16.89430097900707</v>
+        <v>-17.29370782297404</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-13.53557902099296</v>
+        <v>-14.76053217702598</v>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
@@ -5530,16 +5273,16 @@
         <v>15.82106</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1.679360979007053</v>
+        <v>1.266587822974027</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5.195843755245733e-14</v>
+        <v>3.33066907387547e-16</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-17.50042097900706</v>
+        <v>-17.08764782297403</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-14.14169902099295</v>
+        <v>-14.55447217702598</v>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
@@ -6332,28 +6075,28 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>95.48144000000001</v>
+        <v>95.30121999999999</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>80.41724000000001</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>15.0642</v>
+        <v>14.88397999999998</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>15.0642</v>
+        <v>14.88397999999998</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.43186955628634</v>
+        <v>1.473481624690535</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>8.992806499463768e-15</v>
+        <v>1.720845688168993e-14</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>13.63233044371366</v>
+        <v>13.41049837530944</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>16.49606955628634</v>
+        <v>16.35746162469052</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -6374,28 +6117,28 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>95.48144000000001</v>
+        <v>95.30121999999999</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>80.41724000000001</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>15.0642</v>
+        <v>14.88397999999998</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>15.0642</v>
+        <v>14.88397999999998</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1.43186955628634</v>
+        <v>1.473481624690535</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>8.992806499463768e-15</v>
+        <v>1.720845688168993e-14</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>13.63233044371366</v>
+        <v>13.41049837530944</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>16.49606955628634</v>
+        <v>16.35746162469052</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -6416,28 +6159,28 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>95.48144000000001</v>
+        <v>95.30121999999999</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>93.75758</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1.723860000000002</v>
+        <v>1.543639999999982</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>1.723860000000002</v>
+        <v>1.543639999999982</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1.43186955628634</v>
+        <v>1.473481624690535</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.0158181567933583</v>
+        <v>0.03842513475252496</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0.2919904437136618</v>
+        <v>0.07015837530944724</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>3.155729556286342</v>
+        <v>3.017121624690517</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
@@ -6470,16 +6213,16 @@
         <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1.43186955628634</v>
+        <v>1.473481624690535</v>
       </c>
       <c r="H50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-1.43186955628634</v>
+        <v>-1.473481624690535</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>1.43186955628634</v>
+        <v>1.473481624690535</v>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
@@ -6512,16 +6255,16 @@
         <v>13.34034</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>1.43186955628634</v>
+        <v>1.473481624690535</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>6.183942247162122e-14</v>
+        <v>9.692247004977617e-14</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-14.77220955628634</v>
+        <v>-14.81382162469053</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-11.90847044371366</v>
+        <v>-11.86685837530946</v>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
@@ -6554,16 +6297,16 @@
         <v>13.34034</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1.43186955628634</v>
+        <v>1.473481624690535</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>6.183942247162122e-14</v>
+        <v>9.692247004977617e-14</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>-14.77220955628634</v>
+        <v>-14.81382162469053</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-11.90847044371366</v>
+        <v>-11.86685837530946</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
@@ -6588,28 +6331,28 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>90.82626</v>
+        <v>95.89005999999999</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>77.58844000000001</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>13.23782</v>
+        <v>-2.097700000000017</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>13.23782</v>
+        <v>2.097700000000017</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.8758628707987813</v>
+        <v>0.6097823641465648</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0</v>
+        <v>1.902184110225136e-07</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>12.36195712920122</v>
+        <v>-2.707482364146582</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>14.11368287079878</v>
+        <v>-1.487917635853452</v>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
@@ -6618,7 +6361,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>MAPPO</t>
         </is>
       </c>
     </row>
@@ -6630,28 +6373,28 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>90.82626</v>
+        <v>95.89005999999999</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>77.66758000000002</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>13.15867999999999</v>
+        <v>-2.097700000000017</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>13.15867999999999</v>
+        <v>2.097700000000017</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.8758628707987813</v>
+        <v>0.6097823641465648</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>0</v>
+        <v>1.902184110225136e-07</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>12.28281712920121</v>
+        <v>-2.707482364146582</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>14.03454287079877</v>
+        <v>-1.487917635853452</v>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
@@ -6660,7 +6403,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>(s,S) Policy</t>
+          <t>HAPPO</t>
         </is>
       </c>
     </row>
@@ -6672,37 +6415,37 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>90.82626</v>
+        <v>95.89005999999999</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>6.553139999999999</v>
+        <v>-3.877340000000018</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>6.553139999999999</v>
+        <v>3.877340000000018</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.8758628707987813</v>
+        <v>0.6097823641465648</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>1.890043677121866e-12</v>
+        <v>2.311850710867702e-11</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>5.677277129201218</v>
+        <v>-4.487122364146582</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>7.42900287079878</v>
+        <v>-3.267557635853453</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>(s,S) Policy</t>
+      <c r="L55" s="16" t="inlineStr">
+        <is>
+          <t>GNN-HAPPO</t>
         </is>
       </c>
     </row>
@@ -6714,28 +6457,28 @@
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>77.58844000000001</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>77.66758000000002</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>-0.07914000000000954</v>
+        <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.07914000000000954</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.8758628707987813</v>
+        <v>0.6097823641465648</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>0.9936986117520804</v>
+        <v>1</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>-0.9550028707987909</v>
+        <v>-0.6097823641465648</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>0.7967228707987718</v>
+        <v>0.6097823641465648</v>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
@@ -6756,28 +6499,28 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>77.58844000000001</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>-6.68468</v>
+        <v>-1.779640000000001</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>6.68468</v>
+        <v>1.779640000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.8758628707987813</v>
+        <v>0.6097823641465648</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>1.389222070713458e-12</v>
+        <v>1.744558163818688e-06</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>-7.560542870798781</v>
+        <v>-2.389422364146566</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-5.808817129201219</v>
+        <v>-1.169857635853436</v>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
@@ -6798,28 +6541,28 @@
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>77.66758000000002</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>-6.605539999999991</v>
+        <v>-1.779640000000001</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>6.605539999999991</v>
+        <v>1.779640000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.8758628707987813</v>
+        <v>0.6097823641465648</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>1.670774629758398e-12</v>
+        <v>1.744558163818688e-06</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>-7.481402870798772</v>
+        <v>-2.389422364146566</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>-5.729677129201209</v>
+        <v>-1.169857635853436</v>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
@@ -6844,28 +6587,28 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>87.71088</v>
+        <v>87.47286000000001</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>77.61855999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>10.09232000000002</v>
+        <v>9.854300000000023</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>10.09232000000002</v>
+        <v>9.854300000000023</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1.180581977245075</v>
+        <v>1.571174612399856</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>2.37920794177171e-13</v>
+        <v>2.851041625007156e-11</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>8.911738022754941</v>
+        <v>8.283125387600167</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>11.27290197724509</v>
+        <v>11.42547461239988</v>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
@@ -6886,28 +6629,28 @@
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>87.71088</v>
+        <v>87.47286000000001</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>77.50183999999999</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>10.20904000000002</v>
+        <v>9.971020000000024</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>10.20904000000002</v>
+        <v>9.971020000000024</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1.180581977245075</v>
+        <v>1.571174612399856</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>1.988409437103655e-13</v>
+        <v>2.381561614583916e-11</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>9.028458022754942</v>
+        <v>8.399845387600168</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>11.38962197724509</v>
+        <v>11.54219461239988</v>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
@@ -6928,28 +6671,28 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>87.71088</v>
+        <v>87.47286000000001</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>94.87696</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>-7.166079999999994</v>
+        <v>-7.404099999999985</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>7.166079999999994</v>
+        <v>7.404099999999985</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1.180581977245075</v>
+        <v>1.571174612399856</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>4.696565358841553e-11</v>
+        <v>2.097217732810464e-09</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>-8.346661977245068</v>
+        <v>-8.975274612399842</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-5.985498022754919</v>
+        <v>-5.83292538760013</v>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
@@ -6982,16 +6725,16 @@
         <v>0.1167200000000008</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1.180581977245075</v>
+        <v>1.571174612399856</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>0.9917930259679888</v>
+        <v>0.9964643328828754</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>-1.063861977245074</v>
+        <v>-1.454454612399855</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>1.297301977245075</v>
+        <v>1.687894612399856</v>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
@@ -7024,16 +6767,16 @@
         <v>17.25840000000001</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1.180581977245075</v>
+        <v>1.571174612399856</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-15</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>-18.43898197724508</v>
+        <v>-18.82957461239986</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>-16.07781802275493</v>
+        <v>-15.68722538760015</v>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
@@ -7066,16 +6809,16 @@
         <v>17.37512000000001</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1.180581977245075</v>
+        <v>1.571174612399856</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>0</v>
+        <v>3.996802888650564e-15</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>-18.55570197724509</v>
+        <v>-18.94629461239986</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>-16.19453802275493</v>
+        <v>-15.80394538760015</v>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
@@ -7225,34 +6968,34 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>11767.11598</v>
+        <v>55269.7481</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4359.31291184611</v>
+        <v>399.9181018196423</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>19003609.06338821</v>
+        <v>159934.4881630258</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>6936.6421</v>
+        <v>54955.6124</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>15573.6263</v>
+        <v>55856.4083</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>95.52536000000001</v>
+        <v>97.74202</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.6405998618482535</v>
+        <v>0.5015624856386327</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.4103681830000014</v>
+        <v>0.2515649270000036</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>94.6785</v>
+        <v>97.15649999999999</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>96.1442</v>
+        <v>98.35890000000001</v>
       </c>
     </row>
     <row r="6">
@@ -7266,34 +7009,34 @@
         <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>264227.33266</v>
+        <v>65732.06165999999</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>12022.47031019097</v>
+        <v>1054.899613857103</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>144539792.3594232</v>
+        <v>1112813.195315865</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>251976.9471</v>
+        <v>64657.1259</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>280502.0414</v>
+        <v>67224.15760000001</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>76.65346</v>
+        <v>100</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.994506478555532</v>
+        <v>0</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>3.978056092999988</v>
+        <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>74.02500000000001</v>
+        <v>100</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>79.5521</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -7307,34 +7050,34 @@
         <v>5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>262185.04354</v>
+        <v>65769.2102</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>11948.03485310827</v>
+        <v>1061.810739992985</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>142755536.8510899</v>
+        <v>1127442.047564451</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>248989.8342</v>
+        <v>64686.3254</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>280428.6799</v>
+        <v>67275.3553</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>77.84826000000001</v>
+        <v>100</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>2.145666060457688</v>
+        <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4.603882843000012</v>
+        <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>74.4224</v>
+        <v>100</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>80.1319</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -7348,34 +7091,34 @@
         <v>5</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>294123.57576</v>
+        <v>83128.25876</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>12965.51234741584</v>
+        <v>2780.521259968773</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>168104510.4309925</v>
+        <v>7731298.477138332</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>281582.3653</v>
+        <v>79519.21000000001</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>315991.7867</v>
+        <v>86003.7251</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>2.389545825674829</v>
+        <v>0.3075080925764394</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>5.709929253000002</v>
+        <v>0.094561227</v>
       </c>
       <c r="L8" s="20" t="n">
-        <v>57.4001</v>
+        <v>98.1159</v>
       </c>
       <c r="M8" s="20" t="n">
-        <v>63.6452</v>
+        <v>98.92749999999999</v>
       </c>
     </row>
     <row r="9">
@@ -7393,34 +7136,34 @@
         <v>5</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>71590.54244</v>
+        <v>73949.04883999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>8762.430134742581</v>
+        <v>734.3443191900858</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>76780181.86624487</v>
+        <v>539261.5791267506</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>62526.9851</v>
+        <v>73134.618</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>85621.4614</v>
+        <v>74600.15700000001</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.973473637547525</v>
+        <v>0.08852543702236282</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.9476509230000101</v>
+        <v>0.007836753000000326</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>90.50749999999999</v>
+        <v>99.80249999999999</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>92.50660000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -7434,34 +7177,34 @@
         <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>105435.04684</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5233.6398032816</v>
+        <v>235.7054305501574</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>27390985.59049346</v>
+        <v>55557.04999083507</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>96975.68060000001</v>
+        <v>71222.51609999999</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>110531.9235</v>
+        <v>71887.71060000001</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.7242246150194036</v>
+        <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.5245012930000034</v>
+        <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>77.2227</v>
+        <v>100</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>79.17230000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -7475,34 +7218,34 @@
         <v>5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>109947.82728</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>8589.009833161967</v>
+        <v>235.7054305501574</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>73771089.91415296</v>
+        <v>55557.04999083507</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>102136.3529</v>
+        <v>71222.51609999999</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>120436.4608</v>
+        <v>71887.71060000001</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.8055488731293681</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.6489089869999947</v>
+        <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>76.91930000000001</v>
+        <v>100</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>78.9027</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -7516,34 +7259,34 @@
         <v>5</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>116941.21104</v>
+        <v>74449.27092000001</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>6838.034393597838</v>
+        <v>371.6350580504185</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>46758714.36802696</v>
+        <v>138112.6163721379</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>105311.0254</v>
+        <v>74091.1056</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>122048.4074</v>
+        <v>74854.28350000001</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>1.145327715110394</v>
+        <v>0</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>1.311775574999995</v>
+        <v>0</v>
       </c>
       <c r="L12" s="20" t="n">
-        <v>94.75360000000001</v>
+        <v>100</v>
       </c>
       <c r="M12" s="20" t="n">
-        <v>97.9182</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -7561,34 +7304,34 @@
         <v>5</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>174952.73972</v>
+        <v>87473.67942</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>36719.72099765508</v>
+        <v>956.4490000617426</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1348337910.145631</v>
+        <v>914794.6897191072</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>138003.4301</v>
+        <v>86478.21520000001</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>221332.851</v>
+        <v>88934.33319999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>86.72666</v>
+        <v>98.01527999999999</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>2.144783228673703</v>
+        <v>0.3791459244143317</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>4.600095097999995</v>
+        <v>0.1437516319999981</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>83.4426</v>
+        <v>97.4089</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>88.53</v>
+        <v>98.3817</v>
       </c>
     </row>
     <row r="14">
@@ -7602,34 +7345,34 @@
         <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>364807.10478</v>
+        <v>102410.96022</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>10899.90210067903</v>
+        <v>3207.500252482648</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>118807865.8043872</v>
+        <v>10288057.86967625</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>348535.4485</v>
+        <v>97558.2885</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>377078.6918</v>
+        <v>106449.1803</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>79.23348000000001</v>
+        <v>100</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.9273289637447975</v>
+        <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.8599390069999999</v>
+        <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>77.6995</v>
+        <v>100</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>80.05119999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -7643,34 +7386,34 @@
         <v>5</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>367803.24106</v>
+        <v>101424.45222</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>9269.281261966093</v>
+        <v>4178.583039550239</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>85919575.11343573</v>
+        <v>17460556.21841691</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>351724.9921</v>
+        <v>96861.76489999999</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>374573.0088</v>
+        <v>107480.9504</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>79.29212000000001</v>
+        <v>100</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.862403050783098</v>
+        <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.7437390219999948</v>
+        <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>78.06870000000001</v>
+        <v>100</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>80.3947</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -7684,34 +7427,34 @@
         <v>5</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>417673.33198</v>
+        <v>90363.50659999999</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>16830.67770439619</v>
+        <v>442.3430938406009</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>283271711.9892591</v>
+        <v>195667.4126684747</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>400036.4539</v>
+        <v>89742.3722</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>440124.7085</v>
+        <v>90851.30809999999</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>2.957726197098033</v>
+        <v>0</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>8.748144256999989</v>
+        <v>0</v>
       </c>
       <c r="L16" s="20" t="n">
-        <v>76.1135</v>
+        <v>100</v>
       </c>
       <c r="M16" s="20" t="n">
-        <v>83.55459999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -7729,34 +7472,34 @@
         <v>5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>170826.34104</v>
+        <v>243090.99876</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>20353.0668060659</v>
+        <v>16672.27106767002</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>414247328.4121816</v>
+        <v>277964622.5538666</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>140353.8038</v>
+        <v>223494.571</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>193703.9473</v>
+        <v>265165.0017</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>90.72194</v>
+        <v>90.27560000000001</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.097952712096472</v>
+        <v>0.4971575555093183</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1.205500157999998</v>
+        <v>0.2471656350000009</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>89.8002</v>
+        <v>89.5444</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>92.6118</v>
+        <v>90.7649</v>
       </c>
     </row>
     <row r="18">
@@ -7770,34 +7513,34 @@
         <v>5</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>209895.49308</v>
+        <v>226841.5428</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>14444.0976914024</v>
+        <v>14650.99394413196</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>208631958.1187763</v>
+        <v>214651623.5509914</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>196070.6267</v>
+        <v>207675.2124</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>229789.9753</v>
+        <v>245848.3901</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>78.11203999999999</v>
+        <v>77.29986</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.8165520546786948</v>
+        <v>0.3735179888572983</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.6667572579999983</v>
+        <v>0.1395156880000008</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>77.1135</v>
+        <v>76.92440000000001</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>79.2418</v>
+        <v>77.8563</v>
       </c>
     </row>
     <row r="19">
@@ -8401,34 +8144,34 @@
         <v>5</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>56282.888</v>
+        <v>88719.47573999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>5708.317130121548</v>
+        <v>12087.3020614373</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>32584884.4580391</v>
+        <v>146102871.1244265</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>49694.5595</v>
+        <v>75904.46309999999</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>61850.6107</v>
+        <v>107924.222</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>95.48144000000001</v>
+        <v>95.30121999999999</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.1586560210014107</v>
+        <v>0.4157767093044063</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.02517173300000006</v>
+        <v>0.1728702720000008</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>95.3229</v>
+        <v>94.7341</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>95.6919</v>
+        <v>95.7775</v>
       </c>
     </row>
     <row r="34">
@@ -8569,34 +8312,34 @@
         <v>5</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>332468.28218</v>
+        <v>142650.96726</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>15158.5398903619</v>
+        <v>15690.57718531251</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>229781331.6076929</v>
+        <v>246194212.4082493</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>312687.7597</v>
+        <v>130513.2153</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>354370.8627</v>
+        <v>164769.9105</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>90.82626</v>
+        <v>95.89005999999999</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.5208726888597619</v>
+        <v>0.4296120086775985</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.2713083579999983</v>
+        <v>0.184566478000001</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>90.337</v>
+        <v>95.318</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>91.527</v>
+        <v>96.3986</v>
       </c>
     </row>
     <row r="38">
@@ -8610,34 +8353,34 @@
         <v>5</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>431016.02148</v>
+        <v>131516.09112</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>14388.30877945258</v>
+        <v>2488.34464862279</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>207023429.5328723</v>
+        <v>6191859.090329679</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>417050.5175</v>
+        <v>128388.3956</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>454202.4892</v>
+        <v>134763.8676</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>77.58844000000001</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.2878170999089561</v>
+        <v>0.339471630626182</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.08283868300000201</v>
+        <v>0.1152409879999989</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>77.2212</v>
+        <v>97.45310000000001</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>78.00790000000001</v>
+        <v>98.3349</v>
       </c>
     </row>
     <row r="39">
@@ -8651,34 +8394,34 @@
         <v>5</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>411428.11356</v>
+        <v>131516.09112</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>16949.60184162819</v>
+        <v>2488.34464862279</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>287289002.5897258</v>
+        <v>6191859.090329679</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>393598.7179</v>
+        <v>128388.3956</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>432993.4564</v>
+        <v>134763.8676</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>77.66758000000002</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.1742303991845273</v>
+        <v>0.339471630626182</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.03035623199999975</v>
+        <v>0.1152409879999989</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>77.488</v>
+        <v>97.45310000000001</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>77.9152</v>
+        <v>98.3349</v>
       </c>
     </row>
     <row r="40">
@@ -8692,34 +8435,34 @@
         <v>5</v>
       </c>
       <c r="D40" s="19" t="n">
-        <v>388358.1053</v>
+        <v>128190.88714</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>8358.420824673773</v>
+        <v>3094.411974536899</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>69863198.68234017</v>
+        <v>9575385.468157353</v>
       </c>
       <c r="G40" s="19" t="n">
-        <v>375159.0032</v>
+        <v>123292.9924</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>394727.9485</v>
+        <v>131729.2231</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>0.7434331657923281</v>
+        <v>0.1980282555596548</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>0.5526928720000033</v>
+        <v>0.03921518999999996</v>
       </c>
       <c r="L40" s="20" t="n">
-        <v>83.53489999999999</v>
+        <v>99.5539</v>
       </c>
       <c r="M40" s="20" t="n">
-        <v>85.3229</v>
+        <v>99.9567</v>
       </c>
     </row>
     <row r="41">
@@ -8737,34 +8480,34 @@
         <v>5</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>676888.7525199999</v>
+        <v>742692.97098</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>58769.91022575272</v>
+        <v>58649.85711908941</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>3453902347.943034</v>
+        <v>3439805740.089602</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>605454.5876</v>
+        <v>678299.7057</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>731779.3631</v>
+        <v>835505.7077</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>87.71088</v>
+        <v>87.47286000000001</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.8332398256204497</v>
+        <v>1.416817579295231</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.6942886069999974</v>
+        <v>2.007372052999997</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>86.8806</v>
+        <v>85.253</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>88.8329</v>
+        <v>89.0971</v>
       </c>
     </row>
     <row r="42">
@@ -8984,7 +8727,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2.51934790540681e-17</v>
+        <v>8.018936044205768e-14</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -8993,17 +8736,17 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>GNN loses (+2399.5%) ***</t>
+          <t>GNN loses (+50.4%) ***</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>GNN loses (+11.3%) **</t>
+          <t>GNN loses (+26.5%) ***</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>GNN loses (+12.2%) **</t>
+          <t>GNN loses (+26.4%) ***</t>
         </is>
       </c>
     </row>
@@ -9014,26 +8757,26 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2.340856040508056e-07</v>
+        <v>6.037052714383057e-09</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (+63.3%) ***</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>n.s. (+10.9%)</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>n.s. (+6.4%)</t>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>n.s. (+0.7%)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>GNN loses (+4.1%) ***</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>GNN loses (+4.1%) ***</t>
         </is>
       </c>
     </row>
@@ -9044,26 +8787,26 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>2.617799593023155e-11</v>
+        <v>1.136827015018311e-07</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (+138.7%) ***</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (+14.5%) **</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (+13.6%) **</t>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>n.s. (+3.3%)</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>GNN wins (-11.8%) ***</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>GNN wins (-10.9%) ***</t>
         </is>
       </c>
     </row>
@@ -9074,26 +8817,26 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.849406979714727e-05</v>
+        <v>0.006848902972401348</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (+24.2%) **</t>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>GNN wins (-12.7%) *</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>n.s. (+1.1%)</t>
+          <t>n.s. (-6.5%)</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>GNN wins (-15.4%) *</t>
+          <t>GNN wins (-15.4%) **</t>
         </is>
       </c>
     </row>
@@ -9104,7 +8847,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.04100695208333998</v>
+        <v>0.04100695208333996</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
@@ -9134,7 +8877,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>4.349218256529163e-10</v>
+        <v>4.34921825652916e-10</v>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
@@ -9164,7 +8907,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>2.428615467873803e-15</v>
+        <v>2.428615467873804e-15</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
@@ -9194,16 +8937,16 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1.324379816933732e-12</v>
+        <v>1.702748076033798e-10</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (+30.8%) *</t>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>n.s. (-17.0%)</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
@@ -9224,26 +8967,26 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>4.472183354607115e-08</v>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (+16.8%) ***</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>GNN wins (-9.9%) **</t>
+        <v>0.06273371612164513</v>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>ANOVA n.s.</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>ANOVA n.s.</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>n.s. (-5.6%)</t>
+          <t>ANOVA n.s.</t>
         </is>
       </c>
     </row>
@@ -9254,7 +8997,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1695111583228869</v>
+        <v>0.440745358446903</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
@@ -9287,7 +9030,7 @@
       <c r="C16" s="25" t="inlineStr"/>
       <c r="D16" s="26" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
@@ -9297,7 +9040,7 @@
       </c>
       <c r="F16" s="26" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -9347,26 +9090,26 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>4.571158794089305e-14</v>
+        <v>1.686931061659913e-09</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (-35.28pp) ***</t>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>GNN wins (+0.84pp) **</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>GNN loses (-16.41pp) ***</t>
+          <t>GNN loses (-1.42pp) ***</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>GNN loses (-17.60pp) ***</t>
+          <t>GNN loses (-1.42pp) ***</t>
         </is>
       </c>
     </row>
@@ -9377,26 +9120,26 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>4.567371058143465e-16</v>
+        <v>0.002433449089669719</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>**</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>GNN wins (+4.61pp) ***</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>GNN wins (+18.27pp) ***</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>GNN wins (+18.00pp) ***</t>
+          <t>GNN wins (+0.11pp) **</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>n.s. (+0.00pp)</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>n.s. (+0.00pp)</t>
         </is>
       </c>
     </row>
@@ -9407,26 +9150,26 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>1.753970356158491e-05</v>
+        <v>1.274846119172393e-11</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (-7.51pp) ***</t>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>GNN wins (+1.98pp) ***</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>n.s. (-0.02pp)</t>
+          <t>n.s. (+0.00pp)</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>n.s. (-0.08pp)</t>
+          <t>n.s. (+0.00pp)</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9180,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>3.106499663517655e-15</v>
+        <v>2.808934016870164e-17</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
@@ -9446,12 +9189,12 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>GNN wins (+2.61pp) **</t>
+          <t>GNN wins (+3.05pp) ***</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>GNN wins (+15.21pp) ***</t>
+          <t>GNN wins (+16.03pp) ***</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
@@ -9497,7 +9240,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>1.954497005739311e-13</v>
+        <v>1.954497005739312e-13</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
@@ -9527,7 +9270,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>3.584247748157513e-16</v>
+        <v>3.584247748157936e-16</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
@@ -9557,7 +9300,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>2.74900962508139e-16</v>
+        <v>4.837180924804137e-16</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
@@ -9566,7 +9309,7 @@
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>GNN loses (-1.72pp) *</t>
+          <t>GNN loses (-1.54pp) *</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
@@ -9587,26 +9330,26 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>7.397315696309109e-18</v>
+        <v>6.519270865239196e-11</v>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>GNN loses (-6.55pp) ***</t>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>GNN wins (+3.88pp) ***</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>GNN wins (+6.68pp) ***</t>
+          <t>GNN wins (+1.78pp) ***</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>GNN wins (+6.61pp) ***</t>
+          <t>GNN wins (+1.78pp) ***</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9360,7 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>8.435009368259593e-18</v>
+        <v>8.29412493427086e-16</v>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
@@ -9626,7 +9369,7 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>GNN wins (+7.17pp) ***</t>
+          <t>GNN wins (+7.40pp) ***</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
@@ -9650,17 +9393,17 @@
       <c r="C31" s="25" t="inlineStr"/>
       <c r="D31" s="26" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="F31" s="26" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
